--- a/quote_forms/048_lawn_topdressing_quote_request--quote_forms.xlsx
+++ b/quote_forms/048_lawn_topdressing_quote_request--quote_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E30"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="37" customWidth="1" min="2" max="2"/>
-    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -520,12 +520,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>lawn_topdressing_quote_request_form</t>
+          <t>user_name</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Lawn Topdressing Quote Request</t>
+          <t>What is your name?</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -543,12 +543,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>client_name</t>
+          <t>email_address</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>clients_name</t>
+          <t>Email address</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -566,12 +566,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>phone_number</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>Phone number</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -584,17 +584,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>job_type</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>Job Type</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -612,12 +612,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>job_type</t>
+          <t>job_area</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>job_type</t>
+          <t>Job Area</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -630,17 +630,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>service_area</t>
+          <t>schedule_type</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>service_area</t>
+          <t>Schedule</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -653,17 +653,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>schedule_type</t>
+          <t>estimated_job_size</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>schedule_type</t>
+          <t>Estimated Job Size</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -676,17 +676,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>estimated_job_size</t>
+          <t>start_date</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>estimated_job_size</t>
+          <t>Start Date</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -704,12 +704,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>start_date</t>
+          <t>finish_date</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>start_date</t>
+          <t>Finish Date</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -722,17 +722,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>finish_date</t>
+          <t>job_duration</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>finish_date</t>
+          <t>Job Duration</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -745,17 +745,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>job_duration</t>
+          <t>address</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>job_duration</t>
+          <t>Address</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -773,12 +773,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>address</t>
+          <t>follow_up_method</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>address</t>
+          <t>Follow-up Method</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -796,12 +796,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>property_size</t>
+          <t>follow_up_schedule</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>property_size</t>
+          <t>Follow-up Schedule</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -814,17 +814,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>yard_size</t>
+          <t>estimated_job_cost</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>yard_size</t>
+          <t>Estimated Job Cost</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -837,297 +837,21 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>estimated_job_cost</t>
+          <t>payment_terms</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>estimated_job_cost</t>
+          <t>Payment Terms</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>payment_terms</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>payment_terms</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>follow_up_method</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>follow_up_method</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>follow_up_schedule</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>follow_up_schedule</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>notes</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>notes</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>assigned_tool</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>assigned_tool</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>form_id</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>form_id</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>category</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>category</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>assigned_tool</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>assigned_tool</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>category</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>category</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>output_file</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>output_file</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1144,7 +868,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C40"/>
+  <dimension ref="A1:C27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -1194,148 +918,148 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>lawn_renovation</t>
+          <t>landscaping</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Lawn Renovation</t>
+          <t>Landscaping</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>job_type_choices</t>
+          <t>job_area_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>landscaping</t>
+          <t>local</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Landscaping</t>
+          <t>Local</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>job_type_choices</t>
+          <t>job_area_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>fertilization</t>
+          <t>regional</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Fertilization</t>
+          <t>Regional</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>service_area_choices</t>
+          <t>schedule_type_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>one-time</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Local</t>
+          <t>One-time</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>service_area_choices</t>
+          <t>schedule_type_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>regional</t>
+          <t>ongoing</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Regional</t>
+          <t>Ongoing</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>service_area_choices</t>
+          <t>schedule_type_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>state</t>
+          <t>recurring</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>State</t>
+          <t>Recurring</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>schedule_type_choices</t>
+          <t>address_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>one-time</t>
+          <t>single</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>One-time</t>
+          <t>Single</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>schedule_type_choices</t>
+          <t>address_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ongoing</t>
+          <t>duplex</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Ongoing</t>
+          <t>Duplex</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>schedule_type_choices</t>
+          <t>address_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>recurring</t>
+          <t>multi</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Recurring</t>
+          <t>Multi</t>
         </is>
       </c>
     </row>
@@ -1347,12 +1071,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>single</t>
+          <t>single-family</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Single</t>
+          <t>Single-Family</t>
         </is>
       </c>
     </row>
@@ -1364,12 +1088,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>duplex</t>
+          <t>condo</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Duplex</t>
+          <t>Condo</t>
         </is>
       </c>
     </row>
@@ -1381,12 +1105,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>multi</t>
+          <t>townhouse</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Multi</t>
+          <t>Townhouse</t>
         </is>
       </c>
     </row>
@@ -1398,12 +1122,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>single-family</t>
+          <t>apartment</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Single-Family</t>
+          <t>Apartment</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1139,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>condo</t>
+          <t>office_building</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Condo</t>
+          <t>Office Building</t>
         </is>
       </c>
     </row>
@@ -1432,403 +1156,182 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>townhouse</t>
+          <t>farm</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Townhouse</t>
+          <t>Farm</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>address_choices</t>
+          <t>follow_up_method_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>apartment</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Apartment</t>
+          <t>Phone</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>address_choices</t>
+          <t>follow_up_method_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>office_building</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Office Building</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>address_choices</t>
+          <t>follow_up_method_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>farm</t>
+          <t>in-person</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Farm</t>
+          <t>In-person</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>property_size_choices</t>
+          <t>follow_up_schedule_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>small</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Small</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>property_size_choices</t>
+          <t>follow_up_schedule_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Weekly</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>property_size_choices</t>
+          <t>follow_up_schedule_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>large</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>Monthly</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>property_size_choices</t>
+          <t>payment_terms_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>xl</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>XL</t>
+          <t>Cash</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>property_size_choices</t>
+          <t>payment_terms_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>extra_large</t>
+          <t>check</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Extra Large</t>
+          <t>Check</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>yard_size_choices</t>
+          <t>payment_terms_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>small</t>
+          <t>credit_card</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Small</t>
+          <t>Credit Card</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>yard_size_choices</t>
+          <t>payment_terms_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>online_banking</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Medium</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>yard_size_choices</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>large</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Large</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>yard_size_choices</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>xl</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>XL</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>yard_size_choices</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>extra_large</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Extra Large</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>payment_terms_choices</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>cash</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Cash</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>payment_terms_choices</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>check</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Check</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>payment_terms_choices</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>credit_card</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Credit Card</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>payment_terms_choices</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>online_banking</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
           <t>Online Banking</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>follow_up_method_choices</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>phone</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Phone</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>follow_up_method_choices</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>email</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Email</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>follow_up_method_choices</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>in-person</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>In-person</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>follow_up_schedule_choices</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>daily</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Daily</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>follow_up_schedule_choices</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Weekly</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>follow_up_schedule_choices</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Monthly</t>
         </is>
       </c>
     </row>
